--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CACHIMBO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CACHIMBO - 01_02.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAMAGNETRON TITAN CG150/ NXR125-150 90250720</t>
+          <t>CACHIMBO VELA MAGNETRON TITAN CG150/ NXR125-150 90250720</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAPEÇA+ CBX250</t>
+          <t>CACHIMBO VELA PEÇA+ CBX250</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CACHIMBO VELANGK SD05FMGC</t>
+          <t>CACHIMBO VELA NGK SD05FMGC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAMAGNETRON CBX250 2001 A 2008/ CB300 2013 A 2015/ XR250 90250710</t>
+          <t>CACHIMBO VELA MAGNETRON CBX250 2001 A 2008/ CB300 2013 A 2015/ XR250 90250710</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAMAGNETRON TITAN CG FAN150 2014 A 2015/ FAN160 START 2016 90250930</t>
+          <t>CACHIMBO VELA MAGNETRON TITAN CG FAN150 2014 A 2015/ FAN160 START 2016 90250930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAMAGNETRON BIZ100 2005/ CBX200 STRADA/ CG TITAN 1989 90250440</t>
+          <t>CACHIMBO VELA MAGNETRON BIZ100 2005/ CBX200 STRADA/ CG TITAN 1989 90250440</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAMAGNETRON FAN 2009 A 2015/ POP110 2016 A 2024 90250830</t>
+          <t>CACHIMBO VELA MAGNETRON FAN 2009 A 2015/ POP110 2016 A 2024 90250830</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CACHIMBO VELAIRON CG TITAN FAN 120478</t>
+          <t xml:space="preserve"> CACHIMBO VELA IRON CG TITAN FAN 120478</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAIRON CBX250/ XR250 176314</t>
+          <t>CACHIMBO VELA IRON CBX250/ XR250 176314</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CACHIMBO VELAIRON FAZER150/ XTZ150 YBR150/ FACTOR150 188236</t>
+          <t>CACHIMBO VELA IRON FAZER150/ XTZ150 YBR150/ FACTOR150 188236</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CACHIMBO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CACHIMBO - 01_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +492,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,11 +512,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -553,11 +532,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -578,11 +552,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -603,11 +572,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -628,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -649,11 +612,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -674,7 +632,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -687,7 +644,6 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
